--- a/docs/My_Personal_Reviews/UTS-5_skor.xlsx
+++ b/docs/My_Personal_Reviews/UTS-5_skor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rizac\sigma\kominter\all-about-me\My_Personal_Reviews\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3FFAD0-A08F-45C0-BED5-955BCD8A5F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717E1026-0C86-42DF-AF8C-AE4635F4EC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48" yWindow="768" windowWidth="15336" windowHeight="16464" xr2:uid="{8AFE3614-8754-EB4D-B44F-1C12FCF6F8C2}"/>
+    <workbookView xWindow="2976" yWindow="1224" windowWidth="24768" windowHeight="15552" xr2:uid="{8AFE3614-8754-EB4D-B44F-1C12FCF6F8C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="2" r:id="rId1"/>
@@ -916,18 +916,6 @@
       <c r="V3" s="4">
         <v>5</v>
       </c>
-      <c r="W3" s="2">
-        <v>4</v>
-      </c>
-      <c r="X3" s="2">
-        <v>5</v>
-      </c>
-      <c r="Y3" s="2">
-        <v>3</v>
-      </c>
-      <c r="Z3" s="2">
-        <v>4</v>
-      </c>
       <c r="AA3" s="4">
         <v>2</v>
       </c>
